--- a/data/trans_bre/P71_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P71_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 13,29</t>
+          <t>5,02; 13,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 7,11</t>
+          <t>-2,48; 7,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 5,29</t>
+          <t>-5,56; 5,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 7,13</t>
+          <t>-0,59; 7,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,25; 102,93</t>
+          <t>29,74; 106,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 27,28</t>
+          <t>-8,48; 27,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 16,52</t>
+          <t>-14,76; 16,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 71,51</t>
+          <t>-4,27; 76,97</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 13,26</t>
+          <t>5,81; 14,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 4,63</t>
+          <t>-4,33; 4,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 5,14</t>
+          <t>-3,12; 5,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 10,11</t>
+          <t>0,95; 9,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,73; 88,94</t>
+          <t>31,81; 95,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 14,14</t>
+          <t>-11,39; 12,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 15,97</t>
+          <t>-8,58; 16,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,91; 190,81</t>
+          <t>7,5; 179,82</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 15,22</t>
+          <t>6,14; 15,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 6,11</t>
+          <t>-3,73; 6,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 9,92</t>
+          <t>-0,59; 9,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 4,93</t>
+          <t>-8,08; 4,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,97; 87,29</t>
+          <t>28,29; 91,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 18,56</t>
+          <t>-9,86; 18,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 25,29</t>
+          <t>-1,36; 24,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-56,09; 40,24</t>
+          <t>-51,34; 39,41</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,17; 12,82</t>
+          <t>5,22; 12,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 5,17</t>
+          <t>-2,35; 5,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 7,95</t>
+          <t>-0,15; 8,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 22,25</t>
+          <t>1,64; 23,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,12; 68,23</t>
+          <t>22,24; 66,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 24,02</t>
+          <t>-9,19; 26,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 35,59</t>
+          <t>-0,5; 35,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 166,32</t>
+          <t>10,15; 168,94</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,84; 11,97</t>
+          <t>7,68; 11,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,6</t>
+          <t>-1,25; 3,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,75</t>
+          <t>-0,07; 4,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 9,94</t>
+          <t>1,31; 10,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>40,78; 69,44</t>
+          <t>40,33; 69,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 12,28</t>
+          <t>-3,99; 11,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 14,86</t>
+          <t>-0,16; 14,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,46; 83,51</t>
+          <t>10,03; 95,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P71_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P71_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,46</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 13,74</t>
+          <t>5,21; 13,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 7,39</t>
+          <t>-2,66; 6,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 5,08</t>
+          <t>-5,51; 4,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 7,33</t>
+          <t>0,29; 7,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,74; 106,78</t>
+          <t>31,36; 102,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 27,96</t>
+          <t>-8,81; 26,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 16,38</t>
+          <t>-15,49; 15,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 76,97</t>
+          <t>1,43; 67,98</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 14,09</t>
+          <t>5,73; 13,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 4,36</t>
+          <t>-3,83; 4,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 5,3</t>
+          <t>-2,97; 5,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,75</t>
+          <t>-1,61; 4,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,81; 95,46</t>
+          <t>31,03; 86,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 12,93</t>
+          <t>-10,36; 13,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 16,81</t>
+          <t>-8,12; 16,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 179,82</t>
+          <t>-10,62; 38,15</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>3,42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-3,21%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 15,92</t>
+          <t>6,34; 16,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 6,14</t>
+          <t>-3,51; 6,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 9,44</t>
+          <t>-0,93; 9,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 4,98</t>
+          <t>-0,8; 7,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,29; 91,35</t>
+          <t>28,31; 92,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 18,99</t>
+          <t>-9,11; 20,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 24,19</t>
+          <t>-2,13; 24,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-51,34; 39,41</t>
+          <t>-4,61; 60,78</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 12,96</t>
+          <t>5,19; 12,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 5,63</t>
+          <t>-2,81; 5,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 8,04</t>
+          <t>-0,18; 8,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 23,69</t>
+          <t>-1,43; 5,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,24; 66,07</t>
+          <t>22,59; 66,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 26,95</t>
+          <t>-11,26; 25,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 35,83</t>
+          <t>-0,86; 34,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 168,94</t>
+          <t>-8,05; 36,74</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,68; 11,9</t>
+          <t>7,74; 11,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,31</t>
+          <t>-1,36; 3,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,59</t>
+          <t>-0,0; 4,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 10,0</t>
+          <t>0,99; 4,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>40,33; 69,85</t>
+          <t>41,09; 70,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 11,11</t>
+          <t>-4,36; 11,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 14,36</t>
+          <t>-0,12; 13,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,03; 95,2</t>
+          <t>6,37; 32,48</t>
         </is>
       </c>
     </row>
